--- a/main/ig/StructureDefinition-fr-observation-birth-event-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-birth-event-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T10:14:31+00:00</t>
+    <t>2026-07-08T15:46:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-birth-event-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-birth-event-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T15:46:54+00:00</t>
+    <t>2026-07-09T09:13:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-birth-event-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-birth-event-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:13:13+00:00</t>
+    <t>2026-07-10T12:01:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-birth-event-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-birth-event-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T12:01:50+00:00</t>
+    <t>2026-07-10T12:28:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-birth-event-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-birth-event-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T12:28:44+00:00</t>
+    <t>2026-07-10T12:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-birth-event-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-birth-event-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T12:58:40+00:00</t>
+    <t>2026-07-20T14:08:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-birth-event-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-birth-event-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T14:08:41+00:00</t>
+    <t>2026-07-21T09:08:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-birth-event-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-birth-event-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T09:08:11+00:00</t>
+    <t>2026-07-21T09:10:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-birth-event-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-birth-event-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T09:10:59+00:00</t>
+    <t>2026-07-22T09:27:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-birth-event-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-birth-event-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T09:27:19+00:00</t>
+    <t>2026-07-28T07:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-birth-event-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-birth-event-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T07:28:06+00:00</t>
+    <t>2026-07-30T08:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-birth-event-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-birth-event-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T08:11:50+00:00</t>
+    <t>2026-08-03T07:00:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
